--- a/data/trans_dic/P16A_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P16A_R-Clase-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido algún psicofármaco en las dos últimas semanas</t>
+          <t>Población que ha consumido algún psicofármaco en las dos últimas semanas (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,48; 6,42</t>
+          <t>2,57; 6,24</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,95; 7,65</t>
+          <t>2,95; 7,75</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,09; 9,14</t>
+          <t>4,12; 9,05</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,34; 11,13</t>
+          <t>6,34; 11,26</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,8; 10,83</t>
+          <t>4,49; 10,51</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,59; 11,07</t>
+          <t>4,83; 11,34</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,7; 11,85</t>
+          <t>5,48; 11,54</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7,37; 11,85</t>
+          <t>7,47; 11,9</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,87; 7,13</t>
+          <t>3,97; 7,05</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4,22; 8,24</t>
+          <t>4,19; 8,01</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5,24; 9,04</t>
+          <t>5,2; 9,05</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>7,49; 10,82</t>
+          <t>7,32; 10,81</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,5; 7,07</t>
+          <t>2,53; 7,71</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,46; 8,65</t>
+          <t>3,43; 8,59</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,62; 8,55</t>
+          <t>3,44; 8,08</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,76; 9,07</t>
+          <t>4,78; 9,28</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,26; 12,17</t>
+          <t>6,29; 12,32</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,92; 12,82</t>
+          <t>5,98; 12,41</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,13; 9,43</t>
+          <t>3,9; 9,27</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>10,42; 15,76</t>
+          <t>10,72; 15,93</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,94; 8,66</t>
+          <t>4,92; 8,64</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5,16; 9,41</t>
+          <t>5,09; 9,24</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4,27; 7,8</t>
+          <t>4,31; 7,83</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>7,79; 11,27</t>
+          <t>7,96; 11,59</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,71; 7,22</t>
+          <t>3,55; 7,31</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,79; 13,13</t>
+          <t>7,67; 13,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,25; 8,44</t>
+          <t>3,88; 8,11</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,51; 11,6</t>
+          <t>2,53; 11,55</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>8,36; 18,44</t>
+          <t>8,59; 18,76</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>13,77; 23,13</t>
+          <t>13,83; 23,09</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,91; 24,97</t>
+          <t>11,88; 24,39</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>16,96; 26,5</t>
+          <t>16,39; 26,54</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,2; 9,13</t>
+          <t>5,17; 9,11</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>10,04; 15,04</t>
+          <t>10,0; 14,82</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6,81; 11,2</t>
+          <t>6,83; 11,34</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,84; 14,48</t>
+          <t>4,27; 14,29</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,82; 6,33</t>
+          <t>3,85; 6,28</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,59; 8,79</t>
+          <t>5,53; 8,71</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,45; 8,77</t>
+          <t>5,68; 8,6</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7,81; 11,05</t>
+          <t>7,88; 11,11</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,78; 12,16</t>
+          <t>7,92; 12,49</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,17; 16,29</t>
+          <t>11,01; 16,31</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,94; 15,89</t>
+          <t>10,77; 15,66</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6,0; 16,63</t>
+          <t>6,96; 16,52</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,67; 7,94</t>
+          <t>5,64; 7,97</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8,21; 11,12</t>
+          <t>8,33; 11,06</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>8,24; 10,95</t>
+          <t>8,28; 10,97</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>7,83; 12,62</t>
+          <t>7,33; 12,62</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,88; 10,49</t>
+          <t>5,05; 10,33</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,16; 8,15</t>
+          <t>3,98; 8,1</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,86; 10,04</t>
+          <t>5,76; 10,15</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8,63; 14,1</t>
+          <t>8,27; 13,83</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>10,19; 15,99</t>
+          <t>10,7; 16,26</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,98; 22,81</t>
+          <t>17,05; 23,01</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,16; 25,54</t>
+          <t>18,72; 24,98</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>16,72; 26,21</t>
+          <t>17,14; 26,74</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>8,83; 12,97</t>
+          <t>9,14; 13,15</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12,37; 16,56</t>
+          <t>12,44; 16,68</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13,47; 17,56</t>
+          <t>13,62; 17,42</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>15,02; 21,03</t>
+          <t>15,19; 20,78</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,68; 6,22</t>
+          <t>1,81; 6,62</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,06; 5,14</t>
+          <t>1,04; 5,63</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,68; 3,85</t>
+          <t>0,67; 3,87</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2,56; 12,39</t>
+          <t>2,65; 11,54</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>10,58; 14,24</t>
+          <t>10,27; 14,14</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>15,5; 20,29</t>
+          <t>15,5; 20,09</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>15,02; 19,89</t>
+          <t>15,08; 19,77</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>17,75; 22,55</t>
+          <t>17,72; 22,71</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>9,15; 12,33</t>
+          <t>8,99; 12,1</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>12,89; 16,73</t>
+          <t>12,89; 16,82</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>12,14; 16,25</t>
+          <t>12,07; 16,08</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>14,48; 18,64</t>
+          <t>14,61; 18,84</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>4,21; 5,67</t>
+          <t>4,21; 5,7</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>5,7; 7,5</t>
+          <t>5,75; 7,6</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5,48; 7,14</t>
+          <t>5,38; 7,03</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6,37; 9,43</t>
+          <t>6,6; 9,47</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>10,01; 12,07</t>
+          <t>10,08; 12,25</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>14,35; 16,85</t>
+          <t>14,31; 16,86</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>13,9; 16,43</t>
+          <t>13,99; 16,51</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>13,53; 18,14</t>
+          <t>13,64; 18,16</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>7,4; 8,78</t>
+          <t>7,4; 8,76</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>10,42; 12,03</t>
+          <t>10,39; 11,98</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>9,98; 11,63</t>
+          <t>10,12; 11,72</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>10,89; 13,71</t>
+          <t>10,87; 13,53</t>
         </is>
       </c>
     </row>
@@ -1669,7 +1669,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido algún psicofármaco en las dos últimas semanas</t>
+          <t>Población que ha consumido algún psicofármaco en las dos últimas semanas (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>11754; 30438</t>
+          <t>12176; 29546</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>12893; 33437</t>
+          <t>12885; 33876</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>17558; 39240</t>
+          <t>17698; 38812</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>32043; 56247</t>
+          <t>32055; 56868</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>14728; 33208</t>
+          <t>13776; 32240</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>14446; 34812</t>
+          <t>15192; 35654</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>19788; 41120</t>
+          <t>19019; 40048</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>32975; 53035</t>
+          <t>33426; 53233</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>30228; 55660</t>
+          <t>30984; 55039</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>31757; 61970</t>
+          <t>31506; 60223</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>40698; 70147</t>
+          <t>40389; 70233</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>71393; 103052</t>
+          <t>69755; 102987</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9158; 25936</t>
+          <t>9289; 28298</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>14507; 36240</t>
+          <t>14345; 35968</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13661; 32261</t>
+          <t>12966; 30490</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>21539; 41001</t>
+          <t>21596; 41966</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>23261; 45256</t>
+          <t>23380; 45809</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>20017; 43338</t>
+          <t>20223; 41960</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>15361; 35104</t>
+          <t>14511; 34502</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>39848; 60290</t>
+          <t>41025; 60947</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>36463; 63996</t>
+          <t>36327; 63866</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>39078; 71229</t>
+          <t>38529; 69950</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>32016; 58451</t>
+          <t>32336; 58693</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>65033; 94078</t>
+          <t>66449; 96723</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>20109; 39140</t>
+          <t>19247; 39648</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>49028; 82615</t>
+          <t>48265; 81832</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>22174; 44065</t>
+          <t>20240; 42312</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>16778; 77496</t>
+          <t>16878; 77198</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>14021; 30940</t>
+          <t>14421; 31471</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>35832; 60178</t>
+          <t>35988; 60061</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>19790; 41480</t>
+          <t>19744; 40518</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>28315; 44233</t>
+          <t>27361; 44306</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>36926; 64855</t>
+          <t>36715; 64697</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>89341; 133822</t>
+          <t>88946; 131821</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>46868; 77071</t>
+          <t>46980; 77996</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>32046; 120968</t>
+          <t>35642; 119337</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>47305; 78400</t>
+          <t>47698; 77799</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>64838; 101855</t>
+          <t>64114; 100903</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>62622; 100847</t>
+          <t>65324; 98848</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>80869; 114398</t>
+          <t>81570; 114953</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>55559; 86832</t>
+          <t>56537; 89185</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>85599; 124856</t>
+          <t>84376; 125062</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>90389; 131198</t>
+          <t>88978; 129358</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>58663; 162610</t>
+          <t>68036; 161618</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>110671; 154988</t>
+          <t>110075; 155600</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>158036; 214121</t>
+          <t>160350; 212897</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>162714; 216236</t>
+          <t>163630; 216723</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>157643; 254007</t>
+          <t>147637; 254028</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>17095; 36783</t>
+          <t>17703; 36197</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>21221; 41624</t>
+          <t>20319; 41334</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>36369; 62332</t>
+          <t>35735; 63000</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>41000; 66959</t>
+          <t>39263; 65684</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>57968; 90917</t>
+          <t>60858; 92467</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>129332; 173681</t>
+          <t>129808; 175243</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>141477; 188570</t>
+          <t>138236; 184435</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>140705; 220514</t>
+          <t>144214; 224992</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>81146; 119202</t>
+          <t>83997; 120920</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>157306; 210629</t>
+          <t>158197; 212203</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>182987; 238666</t>
+          <t>185074; 236675</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>197680; 276830</t>
+          <t>199966; 273503</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>5003; 18543</t>
+          <t>5403; 19738</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2817; 13712</t>
+          <t>2787; 15034</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1951; 11052</t>
+          <t>1911; 11109</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>6148; 29805</t>
+          <t>6363; 27764</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>132172; 177792</t>
+          <t>128205; 176543</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>171979; 225058</t>
+          <t>171968; 222865</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>162504; 215253</t>
+          <t>163137; 213892</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>135157; 171686</t>
+          <t>134898; 172910</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>141548; 190793</t>
+          <t>139019; 187144</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>177402; 230203</t>
+          <t>177405; 231467</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>166167; 222481</t>
+          <t>165319; 220102</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>145031; 186768</t>
+          <t>146400; 188761</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>137701; 185541</t>
+          <t>137683; 186340</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>195028; 256795</t>
+          <t>196629; 259899</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>185588; 241763</t>
+          <t>182057; 237958</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>215214; 318400</t>
+          <t>222762; 319678</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>338095; 407754</t>
+          <t>340547; 413888</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>509602; 598060</t>
+          <t>507890; 598701</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>490981; 580088</t>
+          <t>494142; 582954</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>484111; 649029</t>
+          <t>488075; 649604</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>492266; 583408</t>
+          <t>491676; 582337</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>726561; 839026</t>
+          <t>724127; 835017</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>690652; 804589</t>
+          <t>700256; 810815</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>757378; 953407</t>
+          <t>756140; 940658</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P16A_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P16A_R-Clase-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>8,67%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,57; 6,24</t>
+          <t>2,54; 6,17</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,95; 7,75</t>
+          <t>3,0; 7,8</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,12; 9,05</t>
+          <t>3,94; 8,87</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,34; 11,26</t>
+          <t>5,94; 10,43</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,49; 10,51</t>
+          <t>4,57; 10,38</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,83; 11,34</t>
+          <t>5,03; 11,09</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,48; 11,54</t>
+          <t>5,35; 11,57</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7,47; 11,9</t>
+          <t>7,51; 11,72</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,97; 7,05</t>
+          <t>3,91; 7,08</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4,19; 8,01</t>
+          <t>4,36; 8,05</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5,2; 9,05</t>
+          <t>5,17; 9,13</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>7,32; 10,81</t>
+          <t>7,12; 10,44</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,53; 7,71</t>
+          <t>2,48; 7,13</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,43; 8,59</t>
+          <t>3,19; 8,57</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,44; 8,08</t>
+          <t>3,44; 8,3</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,78; 9,28</t>
+          <t>4,8; 8,97</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,29; 12,32</t>
+          <t>6,46; 12,31</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,98; 12,41</t>
+          <t>6,07; 12,5</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,9; 9,27</t>
+          <t>3,92; 9,24</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>10,72; 15,93</t>
+          <t>10,47; 15,55</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,92; 8,64</t>
+          <t>5,09; 8,72</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5,09; 9,24</t>
+          <t>5,18; 9,38</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4,31; 7,83</t>
+          <t>4,35; 7,96</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>7,96; 11,59</t>
+          <t>7,99; 11,67</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>20,56%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>13,24%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,55; 7,31</t>
+          <t>3,63; 7,47</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,67; 13,0</t>
+          <t>7,59; 12,69</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,88; 8,11</t>
+          <t>4,19; 8,25</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,53; 11,55</t>
+          <t>7,9; 13,43</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>8,59; 18,76</t>
+          <t>8,22; 18,92</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>13,83; 23,09</t>
+          <t>13,47; 23,19</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,88; 24,39</t>
+          <t>11,82; 24,74</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>16,39; 26,54</t>
+          <t>15,88; 25,85</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,17; 9,11</t>
+          <t>5,33; 9,0</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>10,0; 14,82</t>
+          <t>10,25; 14,92</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6,83; 11,34</t>
+          <t>6,81; 11,48</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4,27; 14,29</t>
+          <t>11,13; 15,66</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>12,01%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,85; 6,28</t>
+          <t>3,73; 6,24</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,53; 8,71</t>
+          <t>5,58; 8,89</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,68; 8,6</t>
+          <t>5,63; 8,7</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7,88; 11,11</t>
+          <t>7,84; 11,14</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,92; 12,49</t>
+          <t>7,83; 12,26</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,01; 16,31</t>
+          <t>11,47; 16,62</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,77; 15,66</t>
+          <t>10,97; 15,48</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6,96; 16,52</t>
+          <t>13,57; 17,53</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,64; 7,97</t>
+          <t>5,53; 7,85</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
+          <t>8,32; 11,16</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
           <t>8,33; 11,06</t>
         </is>
       </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>8,28; 10,97</t>
-        </is>
-      </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>7,33; 12,62</t>
+          <t>10,76; 13,47</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>24,38%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>18,63%</t>
         </is>
       </c>
     </row>
@@ -1277,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,05; 10,33</t>
+          <t>4,9; 10,58</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,98; 8,1</t>
+          <t>4,18; 8,06</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,76; 10,15</t>
+          <t>5,99; 10,36</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8,27; 13,83</t>
+          <t>7,99; 12,9</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>10,7; 16,26</t>
+          <t>10,57; 16,59</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,05; 23,01</t>
+          <t>17,05; 23,14</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,72; 24,98</t>
+          <t>18,96; 25,17</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>17,14; 26,74</t>
+          <t>22,28; 27,0</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>9,14; 13,15</t>
+          <t>8,92; 13,04</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12,44; 16,68</t>
+          <t>12,55; 16,75</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13,62; 17,42</t>
+          <t>13,5; 17,38</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>15,19; 20,78</t>
+          <t>16,86; 20,42</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>19,69%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>16,65%</t>
         </is>
       </c>
     </row>
@@ -1417,52 +1417,52 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,81; 6,62</t>
+          <t>1,8; 6,41</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,04; 5,63</t>
+          <t>1,05; 5,32</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,67; 3,87</t>
+          <t>0,68; 3,98</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2,65; 11,54</t>
+          <t>2,84; 11,34</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>10,27; 14,14</t>
+          <t>10,57; 14,37</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>15,5; 20,09</t>
+          <t>15,59; 20,31</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>15,08; 19,77</t>
+          <t>14,91; 19,95</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>17,72; 22,71</t>
+          <t>17,63; 22,23</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>8,99; 12,1</t>
+          <t>9,18; 12,18</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>12,89; 16,82</t>
+          <t>12,96; 16,89</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>14,61; 18,84</t>
+          <t>14,72; 18,78</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>13,34%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>4,21; 5,7</t>
+          <t>4,18; 5,67</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>5,75; 7,6</t>
+          <t>5,71; 7,58</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5,38; 7,03</t>
+          <t>5,49; 7,2</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6,6; 9,47</t>
+          <t>7,81; 9,71</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>10,08; 12,25</t>
+          <t>10,06; 12,17</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>14,31; 16,86</t>
+          <t>14,34; 16,82</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>13,99; 16,51</t>
+          <t>14,01; 16,53</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>13,64; 18,16</t>
+          <t>16,57; 18,7</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>7,4; 8,76</t>
+          <t>7,41; 8,74</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>10,39; 11,98</t>
+          <t>10,41; 11,98</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>10,12; 11,72</t>
+          <t>10,07; 11,63</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>10,87; 13,53</t>
+          <t>12,57; 14,03</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>42681</t>
+          <t>44279</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>41992</t>
+          <t>45762</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>84673</t>
+          <t>90041</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>12176; 29546</t>
+          <t>12038; 29209</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>12885; 33876</t>
+          <t>13128; 34093</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>17698; 38812</t>
+          <t>16907; 38060</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>32055; 56868</t>
+          <t>32705; 57420</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>13776; 32240</t>
+          <t>14028; 31841</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>15192; 35654</t>
+          <t>15813; 34882</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>19019; 40048</t>
+          <t>18570; 40156</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>33426; 53233</t>
+          <t>36696; 57249</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>30984; 55039</t>
+          <t>30554; 55279</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>31506; 60223</t>
+          <t>32765; 60478</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>40389; 70233</t>
+          <t>40094; 70868</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>69755; 102987</t>
+          <t>73956; 108507</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>30242</t>
+          <t>31712</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>49477</t>
+          <t>54807</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>79719</t>
+          <t>86519</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9289; 28298</t>
+          <t>9103; 26153</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>14345; 35968</t>
+          <t>13369; 35875</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>12966; 30490</t>
+          <t>12966; 31299</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>21596; 41966</t>
+          <t>23183; 43323</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>23380; 45809</t>
+          <t>24022; 45790</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>20223; 41960</t>
+          <t>20526; 42239</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>14511; 34502</t>
+          <t>14589; 34408</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>41025; 60947</t>
+          <t>44309; 65807</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>36327; 63866</t>
+          <t>37576; 64442</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>38529; 69950</t>
+          <t>39208; 70956</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>32336; 58693</t>
+          <t>32587; 59690</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>66449; 96723</t>
+          <t>72439; 105791</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>45424</t>
+          <t>48726</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>35194</t>
+          <t>38558</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>80618</t>
+          <t>87284</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>19247; 39648</t>
+          <t>19697; 40528</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>48265; 81832</t>
+          <t>47790; 79873</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>20240; 42312</t>
+          <t>21891; 43076</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>16878; 77198</t>
+          <t>37248; 63361</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>14421; 31471</t>
+          <t>13800; 31744</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>35988; 60061</t>
+          <t>35038; 60325</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>19744; 40518</t>
+          <t>19638; 41102</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>27361; 44306</t>
+          <t>29780; 48465</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>36715; 64697</t>
+          <t>37835; 63900</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>88946; 131821</t>
+          <t>91164; 132710</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>46980; 77996</t>
+          <t>46873; 79010</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>35642; 119337</t>
+          <t>73365; 103245</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>97060</t>
+          <t>106104</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>121954</t>
+          <t>133334</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>219013</t>
+          <t>239438</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>47698; 77799</t>
+          <t>46182; 77273</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>64114; 100903</t>
+          <t>64688; 103042</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>65324; 98848</t>
+          <t>64683; 100053</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>81570; 114953</t>
+          <t>88693; 126057</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>56537; 89185</t>
+          <t>55895; 87582</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>84376; 125062</t>
+          <t>87901; 127453</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>88978; 129358</t>
+          <t>90612; 127849</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>68036; 161618</t>
+          <t>116877; 150966</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>110075; 155600</t>
+          <t>107960; 153212</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>160350; 212897</t>
+          <t>160195; 214875</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>163630; 216723</t>
+          <t>164513; 218567</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>147637; 254028</t>
+          <t>214445; 268382</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>52433</t>
+          <t>57992</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>190933</t>
+          <t>202564</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>243367</t>
+          <t>260557</t>
         </is>
       </c>
     </row>
@@ -2759,69 +2759,69 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>17703; 36197</t>
+          <t>17163; 37077</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>20319; 41334</t>
+          <t>21330; 41131</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>35735; 63000</t>
+          <t>37206; 64326</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>39263; 65684</t>
+          <t>45390; 73291</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>60858; 92467</t>
+          <t>60101; 94333</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>129808; 175243</t>
+          <t>129866; 176243</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>138236; 184435</t>
+          <t>140008; 185843</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>144214; 224992</t>
+          <t>185126; 224353</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>83997; 120920</t>
+          <t>82044; 119851</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>158197; 212203</t>
+          <t>159678; 213102</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>185074; 236675</t>
+          <t>183503; 236141</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>199966; 273503</t>
+          <t>235890; 285705</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>12583</t>
+          <t>13803</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>152606</t>
+          <t>166267</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>165189</t>
+          <t>180071</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>5403; 19738</t>
+          <t>5375; 19106</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2787; 15034</t>
+          <t>2813; 14202</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1911; 11109</t>
+          <t>1951; 11423</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>6363; 27764</t>
+          <t>6745; 26894</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>128205; 176543</t>
+          <t>132046; 179411</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>171968; 222865</t>
+          <t>172990; 225318</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>163137; 213892</t>
+          <t>161325; 215824</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>134898; 172910</t>
+          <t>148843; 187694</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>139019; 187144</t>
+          <t>142051; 188389</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>177405; 231467</t>
+          <t>178370; 232389</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>165319; 220102</t>
+          <t>165257; 220213</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>146400; 188761</t>
+          <t>159145; 203143</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>280422</t>
+          <t>302617</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>592157</t>
+          <t>641292</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>872578</t>
+          <t>943908</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>137683; 186340</t>
+          <t>136820; 185420</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>196629; 259899</t>
+          <t>195556; 259231</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>182057; 237958</t>
+          <t>185997; 243932</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>222762; 319678</t>
+          <t>268967; 334207</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>340547; 413888</t>
+          <t>339864; 411282</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>507890; 598701</t>
+          <t>509160; 597297</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>494142; 582954</t>
+          <t>494851; 583941</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>488075; 649604</t>
+          <t>602456; 679772</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>491676; 582337</t>
+          <t>492741; 581184</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>724127; 835017</t>
+          <t>725819; 835219</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>700256; 810815</t>
+          <t>696825; 804587</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>756140; 940658</t>
+          <t>889792; 993101</t>
         </is>
       </c>
     </row>
